--- a/data/trans_orig/IP19C04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54268</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43794</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48680</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95687</t>
+          <t>95615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102656</t>
+          <t>102330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>39758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>30806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68119</t>
+          <t>67964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75433</t>
+          <t>75327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34348</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45811</t>
+          <t>45896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52017</t>
+          <t>52012</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77850</t>
+          <t>77383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86087</t>
+          <t>85596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87071</t>
+          <t>86364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95271</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84808</t>
+          <t>84700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93343</t>
+          <t>93190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175252</t>
+          <t>175560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186913</t>
+          <t>186735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>49180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59568</t>
+          <t>60107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67249</t>
+          <t>67228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112094</t>
+          <t>111327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120874</t>
+          <t>120774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>34623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35068</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67341</t>
+          <t>66889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>73796</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31411</t>
+          <t>30803</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31126</t>
+          <t>30340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50300</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>299102</t>
+          <t>299051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311887</t>
+          <t>312165</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310277</t>
+          <t>310885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>325345</t>
+          <t>326036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614486</t>
+          <t>615207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>633660</t>
+          <t>634446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>44778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35362</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>40306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83049</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88473</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>42227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95832</t>
+          <t>95214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39081</t>
+          <t>39161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75314</t>
+          <t>75222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80807</t>
+          <t>80790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77722</t>
+          <t>77892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87133</t>
+          <t>86923</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84937</t>
+          <t>84726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94475</t>
+          <t>94507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167087</t>
+          <t>167012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179740</t>
+          <t>179883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65979</t>
+          <t>66509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76336</t>
+          <t>76261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63587</t>
+          <t>63124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71603</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133392</t>
+          <t>132555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145793</t>
+          <t>145555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32153</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56405</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61939</t>
+          <t>61941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51097</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>305987</t>
+          <t>306512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>321323</t>
+          <t>321357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>316541</t>
+          <t>315833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330537</t>
+          <t>330326</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628407</t>
+          <t>629037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>648645</t>
+          <t>649388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88209</t>
+          <t>87867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>51598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48230</t>
+          <t>48099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53383</t>
+          <t>53397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102002</t>
+          <t>102435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>108435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>29858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>30910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56913</t>
+          <t>56869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64152</t>
+          <t>64028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100365</t>
+          <t>100026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108263</t>
+          <t>108021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95780</t>
+          <t>95403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102489</t>
+          <t>102003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199366</t>
+          <t>199384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209091</t>
+          <t>209244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60405</t>
+          <t>60780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67590</t>
+          <t>67664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67685</t>
+          <t>67919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131305</t>
+          <t>131529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140098</t>
+          <t>140306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22736</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>30539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54950</t>
+          <t>55011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62582</t>
+          <t>62583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>42854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>317302</t>
+          <t>318036</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>331445</t>
+          <t>331453</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>328217</t>
+          <t>328672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>340674</t>
+          <t>341113</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>651196</t>
+          <t>649588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>668574</t>
+          <t>668509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63079</t>
+          <t>63503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70016</t>
+          <t>69947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90665</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157129</t>
+          <t>156068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165001</t>
+          <t>165107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59323</t>
+          <t>58995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66698</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127924</t>
+          <t>127390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133569</t>
+          <t>133577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>35551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56529</t>
+          <t>56482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63438</t>
+          <t>63403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100487</t>
+          <t>100267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108838</t>
+          <t>108631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116337</t>
+          <t>116367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125139</t>
+          <t>125037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220896</t>
+          <t>219799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232045</t>
+          <t>232371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60075</t>
+          <t>59984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67007</t>
+          <t>66916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97693</t>
+          <t>97566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>161198</t>
+          <t>160803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169774</t>
+          <t>169354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>38002</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76908</t>
+          <t>76623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87280</t>
+          <t>87693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43267</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>359105</t>
+          <t>359924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>374363</t>
+          <t>374821</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>457334</t>
+          <t>456523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>470689</t>
+          <t>470446</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>822211</t>
+          <t>821254</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>842073</t>
+          <t>841346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
